--- a/tableau-synthese-e5.xlsx
+++ b/tableau-synthese-e5.xlsx
@@ -8,10 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Tableau de synthèse Épreuve E4'!$A$1:$H$35</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">AP 2 – Évolution de l'infrastructure pour un nouveau client : service de fichiers Windows Server, GPO, stockage iSCSI, scripts Powershell, VyOS, comptes-rendus de test, documentations techniques.</t>
   </si>
   <si>
-    <t xml:space="preserve">AP 4 – Sécurisation de l'infrastructure réseau :  VLAN, routage interVLAN sur Packet Tracer Syslog sur Windows Server ; VyOS ; comptes-rendus de test, documentations techniques.</t>
+    <t xml:space="preserve">AP 3 – Sécurisation de l'infrastructure réseau :  VLAN, routage interVLAN sur Packet Tracer Syslog sur Windows Server ; VyOS ; comptes-rendus de test, documentations techniques.</t>
   </si>
   <si>
     <t xml:space="preserve">  SÉQUENCES DE FORMATION (1re et 2e année)</t>
@@ -372,6 +372,7 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
